--- a/docs/工作量.xlsx
+++ b/docs/工作量.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27611" windowHeight="14064"/>
+    <workbookView windowWidth="30623" windowHeight="14064"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
     <t>CRF 填审</t>
   </si>
   <si>
-    <t>模板引擎配置、模块侧栏与字段过滤、字段卡片控件渲染、状态流转与提交、来源证据抽屉</t>
+    <t>模板引擎配置、表单设计、状态流转与提交、来源证据抽屉</t>
   </si>
   <si>
     <t>字段映射</t>
@@ -79,7 +79,7 @@
     <t>导出中心</t>
   </si>
   <si>
-    <t>导出预设界面、后端导出引擎（CSV/EXCEL/ 文件打包）、历史记录</t>
+    <t>.</t>
   </si>
   <si>
     <t>首页与入口</t>
@@ -112,9 +112,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -133,37 +133,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -171,29 +195,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -207,53 +208,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -269,16 +223,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,19 +294,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,73 +444,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,85 +456,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -502,76 +503,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -594,156 +530,221 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -755,14 +756,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1108,7 +1109,7 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1119,16 +1120,16 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>15</v>
       </c>
     </row>
@@ -1136,7 +1137,7 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1150,7 +1151,7 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1164,7 +1165,7 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1178,7 +1179,7 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1192,7 +1193,7 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1206,7 +1207,7 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1220,7 +1221,7 @@
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1234,7 +1235,7 @@
       <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1248,7 +1249,7 @@
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1262,7 +1263,7 @@
       <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">

--- a/docs/工作量.xlsx
+++ b/docs/工作量.xlsx
@@ -37,7 +37,7 @@
     <t>设备对接，数据蒸馏</t>
   </si>
   <si>
-    <t>对接常见设备，开发接口，提取文件</t>
+    <t>对接常见设备，开发接口，提取文件，非结构化治理</t>
   </si>
   <si>
     <t>数据来源与治理</t>
@@ -79,7 +79,7 @@
     <t>导出中心</t>
   </si>
   <si>
-    <t>.</t>
+    <t>导出预览，支持excel,csv导出</t>
   </si>
   <si>
     <t>首页与入口</t>
@@ -111,10 +111,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -141,6 +141,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -149,6 +171,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -156,14 +186,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -171,7 +194,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,16 +216,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -208,11 +254,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -223,63 +277,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,12 +294,180 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -307,174 +475,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,39 +503,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -547,6 +514,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,11 +559,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -586,16 +575,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -606,10 +606,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -618,133 +618,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
